--- a/output/pdf_financials_xlsx/ATMY.xlsx
+++ b/output/pdf_financials_xlsx/ATMY.xlsx
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.348497</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.623667</v>
       </c>
     </row>
     <row r="93">
@@ -1974,7 +1974,7 @@
         <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-1.034896</v>
       </c>
     </row>
     <row r="119">
@@ -2572,7 +2572,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" s="5" t="n">
         <v>0.348497</v>
       </c>
@@ -2942,7 +2946,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ATMY.xlsx
+++ b/output/pdf_financials_xlsx/ATMY.xlsx
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>0.071586</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.161913</v>
       </c>
     </row>
     <row r="102">
@@ -1815,10 +1815,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.101884</v>
+        <v>0.17347</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.042863</v>
+        <v>-0.11905</v>
       </c>
     </row>
     <row r="107">
@@ -2814,7 +2814,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="n">
         <v>0.071586</v>
       </c>
